--- a/data/marsh edge (raw).xlsx
+++ b/data/marsh edge (raw).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="368" documentId="8_{F8D09033-D556-4131-9203-923A62BF7BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32D32727-B679-4DD7-BDB0-379B5B775EA5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4390205D-7EAD-425A-9D36-DFA78AD01DEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4390205D-7EAD-425A-9D36-DFA78AD01DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="marsh_edge" sheetId="1" r:id="rId1"/>

--- a/data/marsh edge (raw).xlsx
+++ b/data/marsh edge (raw).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="8_{F8D09033-D556-4131-9203-923A62BF7BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32D32727-B679-4DD7-BDB0-379B5B775EA5}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="8_{F8D09033-D556-4131-9203-923A62BF7BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33351D68-62A3-4ED1-AEDE-782302D8F56E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4390205D-7EAD-425A-9D36-DFA78AD01DEC}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{4390205D-7EAD-425A-9D36-DFA78AD01DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="marsh_edge" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="45">
   <si>
     <t>N/A</t>
   </si>
@@ -208,9 +208,6 @@
     <t>Not measured</t>
   </si>
   <si>
-    <t xml:space="preserve">Marsh edge completely eroded-measurement pic took at 0.5 pole; 0.5 samples lost </t>
-  </si>
-  <si>
     <t>scarp-large overhang, hard to tell; pickleweed-none observed lots of jawmea</t>
   </si>
   <si>
@@ -248,6 +245,18 @@
   </si>
   <si>
     <t>(1 ruler length) + 29</t>
+  </si>
+  <si>
+    <t>two measurements-for scarp, 118 and 140 cm has a horseshoe shape; pickleweed reaches beyond the scarp limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scarpe-very sloped hard to measure </t>
+  </si>
+  <si>
+    <t>Marsh edge completely eroded-measurement pic took at 0.5 pole; 0.5 samples lost; for scarp measurement subtracted 50 to get to the scarp measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 meter pole eroded-scarp measurement completed from the 2 meter pole, so add the measurement plus the 147 cm, 147 cm would be close to the 0.5 cm pole within 3 cm, so subtracted 3 </t>
   </si>
 </sst>
 </file>
@@ -376,10 +385,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -965,25 +970,34 @@
       <c r="B13">
         <v>1</v>
       </c>
+      <c r="C13" s="3">
+        <v>46212</v>
+      </c>
       <c r="D13" t="s">
         <v>1</v>
       </c>
       <c r="E13" t="s">
         <v>0</v>
+      </c>
+      <c r="F13">
+        <v>125</v>
+      </c>
+      <c r="G13">
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="12" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="13"/>
       <c r="F14" s="12">
-        <f>F12-F6</f>
-        <v>-74</v>
+        <f>F13-F6</f>
+        <v>10</v>
       </c>
       <c r="G14" s="12">
-        <f>G12-G6</f>
-        <v>-38</v>
+        <f>G13-G6</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1140,7 +1154,7 @@
         <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1219,25 +1233,34 @@
       <c r="B26">
         <v>2</v>
       </c>
+      <c r="C26" s="3">
+        <v>46212</v>
+      </c>
       <c r="D26" t="s">
         <v>1</v>
       </c>
       <c r="E26" t="s">
         <v>0</v>
+      </c>
+      <c r="F26">
+        <v>115</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="8" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="9"/>
       <c r="F27" s="8">
-        <f>F25-F19</f>
-        <v>14</v>
+        <f>F26-F19</f>
+        <v>16</v>
       </c>
       <c r="G27" s="8">
-        <f>G25-G19</f>
-        <v>3</v>
+        <f>G26-G19</f>
+        <v>-17</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -1379,16 +1402,16 @@
         <v>6</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -1414,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1473,26 +1496,41 @@
       <c r="B39">
         <v>1</v>
       </c>
+      <c r="C39" s="3">
+        <v>46210</v>
+      </c>
       <c r="D39" t="s">
         <v>1</v>
+      </c>
+      <c r="E39">
+        <v>140</v>
+      </c>
+      <c r="F39">
+        <v>104</v>
+      </c>
+      <c r="G39">
+        <v>143</v>
+      </c>
+      <c r="I39" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="8" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="9"/>
       <c r="E40" s="8">
-        <f>E38-E28</f>
-        <v>-38</v>
-      </c>
-      <c r="F40" s="8" t="e">
-        <f>F38-F28</f>
-        <v>#VALUE!</v>
+        <f>E39-E28</f>
+        <v>-15</v>
+      </c>
+      <c r="F40" s="8">
+        <f>F39-F28</f>
+        <v>8</v>
       </c>
       <c r="G40" s="8">
-        <f>G38-G28</f>
-        <v>9</v>
+        <f>G39-G28</f>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -1509,7 +1547,7 @@
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -1637,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -1663,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
@@ -1689,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
@@ -1725,26 +1763,40 @@
       <c r="B52">
         <v>2</v>
       </c>
+      <c r="C52" s="3">
+        <v>46210</v>
+      </c>
       <c r="D52" t="s">
         <v>1</v>
+      </c>
+      <c r="E52">
+        <v>124</v>
+      </c>
+      <c r="F52">
+        <v>74</v>
+      </c>
+      <c r="G52" t="s">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="8" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C53" s="9"/>
       <c r="E53" s="8">
-        <f>E51-E45</f>
-        <v>-7</v>
+        <f>E52-E45</f>
+        <v>-1</v>
       </c>
       <c r="F53" s="8">
-        <f>F51-F45</f>
-        <v>-28</v>
-      </c>
-      <c r="G53" s="8" t="e">
-        <f>G51-G45</f>
-        <v>#VALUE!</v>
+        <f>F52-F45</f>
+        <v>-44</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -1844,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
@@ -1907,10 +1959,10 @@
         <v>6</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>0</v>
@@ -1992,26 +2044,37 @@
       <c r="B65">
         <v>1</v>
       </c>
+      <c r="C65" s="3">
+        <v>46211</v>
+      </c>
       <c r="D65" t="s">
         <v>1</v>
+      </c>
+      <c r="E65">
+        <v>97</v>
+      </c>
+      <c r="F65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="8" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" s="9"/>
       <c r="E66" s="8">
-        <f>E63-E54</f>
-        <v>-14</v>
+        <f>E65-E54</f>
+        <v>-56</v>
       </c>
       <c r="F66" s="8">
         <f>F63-F54</f>
         <v>-14</v>
       </c>
-      <c r="G66" s="8" t="e">
-        <f>G63-G54</f>
-        <v>#VALUE!</v>
+      <c r="G66" s="8" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
@@ -2037,7 +2100,7 @@
         <v>53</v>
       </c>
       <c r="J67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
@@ -2243,7 +2306,8 @@
         <v>3</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <f>17-50</f>
+        <v>-33</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2252,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2262,22 +2326,38 @@
       <c r="B78">
         <v>2</v>
       </c>
+      <c r="C78" s="3">
+        <v>46211</v>
+      </c>
       <c r="D78" t="s">
         <v>1</v>
+      </c>
+      <c r="E78">
+        <f>E77-3</f>
+        <v>-36</v>
+      </c>
+      <c r="F78" t="s">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="8" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C79" s="9"/>
       <c r="E79" s="8">
-        <f>E77-E67</f>
-        <v>-210</v>
+        <f>E78-E67</f>
+        <v>-246</v>
       </c>
       <c r="F79" s="8">
-        <f>F77-F67</f>
-        <v>-120</v>
+        <f ca="1">F79-F67</f>
+        <v>0</v>
       </c>
       <c r="G79" s="8">
         <f>G77-G67</f>
@@ -2511,25 +2591,34 @@
       <c r="B91">
         <v>1</v>
       </c>
+      <c r="C91" s="3">
+        <v>46209</v>
+      </c>
       <c r="D91" t="s">
         <v>1</v>
       </c>
       <c r="E91" t="s">
         <v>0</v>
+      </c>
+      <c r="F91">
+        <v>634</v>
+      </c>
+      <c r="G91">
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="8" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C92" s="9"/>
       <c r="F92" s="8">
-        <f>F90-F84</f>
+        <f>F91-F84</f>
+        <v>-46</v>
+      </c>
+      <c r="G92" s="8">
+        <f>G91-G84</f>
         <v>4</v>
-      </c>
-      <c r="G92" s="8">
-        <f>G90-G84</f>
-        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -2762,24 +2851,33 @@
       <c r="B104">
         <v>2</v>
       </c>
+      <c r="C104" s="3">
+        <v>46209</v>
+      </c>
       <c r="D104" t="s">
         <v>1</v>
       </c>
       <c r="E104" t="s">
         <v>0</v>
+      </c>
+      <c r="F104">
+        <v>600</v>
+      </c>
+      <c r="G104">
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="10" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C105" s="11"/>
-      <c r="F105" s="10">
-        <f>F103-F97</f>
-        <v>-10</v>
-      </c>
-      <c r="G105" s="10">
-        <f>G103-G97</f>
+      <c r="F105" s="8">
+        <f>F104-F97</f>
+        <v>-145</v>
+      </c>
+      <c r="G105" s="8">
+        <f>G104-G97</f>
         <v>2</v>
       </c>
     </row>
@@ -2790,6 +2888,7 @@
     <sortCondition ref="C2:C104"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/marsh edge (raw).xlsx
+++ b/data/marsh edge (raw).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="8_{F8D09033-D556-4131-9203-923A62BF7BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33351D68-62A3-4ED1-AEDE-782302D8F56E}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="8_{F8D09033-D556-4131-9203-923A62BF7BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B429D05-BF16-481A-8AC7-5AA59352186A}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{4390205D-7EAD-425A-9D36-DFA78AD01DEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4390205D-7EAD-425A-9D36-DFA78AD01DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="marsh_edge" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="46">
   <si>
     <t>N/A</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.5 meter pole eroded-scarp measurement completed from the 2 meter pole, so add the measurement plus the 147 cm, 147 cm would be close to the 0.5 cm pole within 3 cm, so subtracted 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">found on iphone notes app </t>
   </si>
 </sst>
 </file>
@@ -385,6 +388,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1327,6 +1334,15 @@
       <c r="D31" t="s">
         <v>10</v>
       </c>
+      <c r="E31">
+        <v>138</v>
+      </c>
+      <c r="F31">
+        <v>98</v>
+      </c>
+      <c r="H31" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
